--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>79.11303733477276</v>
+        <v>12.85586856690057</v>
       </c>
       <c r="D2" t="n">
-        <v>77.73585342718661</v>
+        <v>12.63207618191782</v>
       </c>
       <c r="E2" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F2" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>110.1569112268856</v>
+        <v>17.90049807436892</v>
       </c>
       <c r="D3" t="n">
-        <v>110.2742639750175</v>
+        <v>17.91956789594035</v>
       </c>
       <c r="E3" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F3" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>81.24529185909191</v>
+        <v>13.20235992710244</v>
       </c>
       <c r="D4" t="n">
-        <v>79.67301460525124</v>
+        <v>12.94686487335333</v>
       </c>
       <c r="E4" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F4" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>82.43113238649143</v>
+        <v>13.39505901280486</v>
       </c>
       <c r="D5" t="n">
-        <v>82.17333385938939</v>
+        <v>13.35316675215078</v>
       </c>
       <c r="E5" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F5" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>101.3507927987165</v>
+        <v>16.46950382979142</v>
       </c>
       <c r="D6" t="n">
-        <v>101.5252059654766</v>
+        <v>16.49784596938994</v>
       </c>
       <c r="E6" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F6" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>66.29706970958367</v>
+        <v>10.77327382780735</v>
       </c>
       <c r="D7" t="n">
-        <v>64.86237484837288</v>
+        <v>10.54013591286059</v>
       </c>
       <c r="E7" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F7" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>95.0654771849353</v>
+        <v>15.44814004255199</v>
       </c>
       <c r="D8" t="n">
-        <v>95.26063702802381</v>
+        <v>15.47985351705387</v>
       </c>
       <c r="E8" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F8" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>64.87060492195293</v>
+        <v>10.54147329981735</v>
       </c>
       <c r="D9" t="n">
-        <v>63.572096705035</v>
+        <v>10.33046571456819</v>
       </c>
       <c r="E9" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F9" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>88.41357870512736</v>
+        <v>14.3672065395832</v>
       </c>
       <c r="D10" t="n">
-        <v>86.8028029577665</v>
+        <v>14.10545548063706</v>
       </c>
       <c r="E10" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F10" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>78.95127981443169</v>
+        <v>12.82958296984515</v>
       </c>
       <c r="D11" t="n">
-        <v>77.34508335272305</v>
+        <v>12.5685760448175</v>
       </c>
       <c r="E11" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F11" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>71.18500217548083</v>
+        <v>11.56756285351564</v>
       </c>
       <c r="D12" t="n">
-        <v>69.59144059381548</v>
+        <v>11.30860909649502</v>
       </c>
       <c r="E12" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F12" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>91.43664526857258</v>
+        <v>14.85845485614304</v>
       </c>
       <c r="D13" t="n">
-        <v>92.01203789721099</v>
+        <v>14.95195615829679</v>
       </c>
       <c r="E13" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F13" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>68.66763487145977</v>
+        <v>11.15849066661221</v>
       </c>
       <c r="D14" t="n">
-        <v>67.10728114318017</v>
+        <v>10.90493318576678</v>
       </c>
       <c r="E14" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F14" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>82.82412657838385</v>
+        <v>13.45892056898738</v>
       </c>
       <c r="D15" t="n">
-        <v>83.62639535905085</v>
+        <v>13.58928924584576</v>
       </c>
       <c r="E15" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F15" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>66.70760792585561</v>
+        <v>10.83998628795154</v>
       </c>
       <c r="D16" t="n">
-        <v>65.30575134257859</v>
+        <v>10.61218459316902</v>
       </c>
       <c r="E16" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F16" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>52.81603389385901</v>
+        <v>8.58260550775209</v>
       </c>
       <c r="D17" t="n">
-        <v>51.52620339431692</v>
+        <v>8.3730080515765</v>
       </c>
       <c r="E17" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F17" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>62.79553672156128</v>
+        <v>10.20427471725371</v>
       </c>
       <c r="D18" t="n">
-        <v>61.69103261027369</v>
+        <v>10.02479279916948</v>
       </c>
       <c r="E18" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F18" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>73.37653296570529</v>
+        <v>11.92368660692711</v>
       </c>
       <c r="D19" t="n">
-        <v>74.17666572099267</v>
+        <v>12.05370817966131</v>
       </c>
       <c r="E19" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F19" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>70.82091596057884</v>
+        <v>11.50839884359406</v>
       </c>
       <c r="D20" t="n">
-        <v>71.82395654719207</v>
+        <v>11.67139293891871</v>
       </c>
       <c r="E20" t="n">
-        <v>13.99549437639912</v>
+        <v>2.274267836164857</v>
       </c>
       <c r="F20" t="n">
-        <v>14.45176289491718</v>
+        <v>2.348411470424041</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
